--- a/reports/devops-jobs-israel-2026-W25.xlsx
+++ b/reports/devops-jobs-israel-2026-W25.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="535">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-15T12:37:22</t>
+    <t xml:space="preserve">2026-06-16T11:29:24</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8%</t>
+    <t xml:space="preserve">1.7%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -306,6 +306,18 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
   </si>
   <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
   </si>
   <si>
@@ -579,15 +591,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
-    <t xml:space="preserve">Product Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Devops Engineer</t>
   </si>
   <si>
@@ -603,1012 +606,988 @@
     <t xml:space="preserve">2026-06-15</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA AI</t>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4428872095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36609)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36609-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428812089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4425737474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-global-e-4425722658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4425736215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-STAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-g-stat-4427413680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-compie-technologies-4428808414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4425723456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infotree Global Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Semiconductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4425760569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4428621761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group (Copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-copy-at-bigpanda-4427444455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentee Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aman Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4423678087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer | AWS | Kubernetes | Hybrid | Tel Aviv Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T&amp;S Talents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-aws-kubernetes-hybrid-tel-aviv-area-at-t-s-talents-4414893892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Software Engineer - SAP Cloud Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4422246034</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-software-engineer-sap-cloud-virtualization-at-sap-4417871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bynet-data-communications-4423131095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4427729203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpticSolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-opticsolution-4427439160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (36613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYL Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-dyl-group-4428654157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psistar (Maverick AI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-infrastructure-engineer-at-psistar-maverick-ai-4426497175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer - Electronic Warfare Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-electronic-warfare-systems-at-regulus-4427439098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Squad Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Hai, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tikal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tikal-4425757948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIGO Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stampli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-nexite-4425654229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest acq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4427190837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36609)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36609-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428812089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4425737474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-devops-engineer-at-teads-4356546289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoIP/DevOps Engineer (SIP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squaretalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/voip-devops-engineer-sip-focus-at-squaretalk-4426348262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-abra-4425998329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4428678465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4425736215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-compie-technologies-4428808414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentee Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aman Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4423678087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25078)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aqua Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aqua-security-4418683555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4425760569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4427161800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4416227220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz (part of Google Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-part-of-google-cloud-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4428621761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-unity-4428813920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Infrastructure Engineer（SRE）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社GA technologies / GA technologies Co., Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-infrastructure-engineer%EF%BC%88sre%EF%BC%89-at-%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BEga-technologies-ga-technologies-co-ltd-4425654538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tikal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tikal-4425757948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CorrActions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-devops-engineer-at-corractions-4423612672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4425723456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-part-of-google-cloud-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-STAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-g-stat-4427413680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-platform-engineer-at-gotfriends-4421571443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8 Stealth Mode Startup-Senior Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team8-stealth-mode-startup-senior-infra-engineer-at-team8-4427476799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4426102112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4425749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4425237881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-infrastructure-engineer-at-comblack-4425497939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Squad Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ur-tech-jobs-4425565373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIGO Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4425741384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4408743594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Product Operations – Part-Time Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-product-operations-%E2%80%93-part-time-student-at-finout-4427681349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1769,7 +1748,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -1777,7 +1756,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1785,7 +1764,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1793,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>607</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10">
@@ -1801,7 +1780,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1865,7 +1844,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
@@ -1892,36 +1871,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1929,7 +1908,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1948,111 +1927,111 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>431</v>
+        <v>520</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>429</v>
+        <v>257</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>530</v>
+        <v>417</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>286</v>
+        <v>523</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>532</v>
+        <v>414</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -2060,18 +2039,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>421</v>
+        <v>525</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2096,13 +2075,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2">
@@ -2113,10 +2092,10 @@
         <v>43</v>
       </c>
       <c r="C2" s="3">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2128,85 +2107,85 @@
         <v>82</v>
       </c>
       <c r="C3" s="3">
-        <v>34.7</v>
+        <v>36.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>9.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>29.3</v>
+        <v>31.4</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2217,8 +2196,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="49" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2290,7 +2269,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -2322,7 +2301,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -2354,7 +2333,7 @@
         <v>48</v>
       </c>
       <c r="J4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2386,7 +2365,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2418,7 +2397,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2450,7 +2429,7 @@
         <v>48</v>
       </c>
       <c r="J7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2482,7 +2461,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -2514,7 +2493,7 @@
         <v>65</v>
       </c>
       <c r="J9" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -2546,7 +2525,7 @@
         <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -2578,7 +2557,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -2610,7 +2589,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -2642,7 +2621,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -2674,7 +2653,7 @@
         <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -2706,7 +2685,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2738,7 +2717,7 @@
         <v>90</v>
       </c>
       <c r="J16" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -2770,7 +2749,7 @@
         <v>41</v>
       </c>
       <c r="J17" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -2778,39 +2757,39 @@
         <v>95</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J18" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>59</v>
@@ -2822,27 +2801,27 @@
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J19" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>59</v>
@@ -2866,7 +2845,7 @@
         <v>106</v>
       </c>
       <c r="J20" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2874,7 +2853,7 @@
         <v>107</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>59</v>
@@ -2895,18 +2874,18 @@
         <v>109</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="J21" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>59</v>
@@ -2918,30 +2897,30 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="J22" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>59</v>
@@ -2959,59 +2938,59 @@
         <v>116</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="J23" s="3">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J24" s="3">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>124</v>
@@ -3023,24 +3002,24 @@
         <v>125</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="J25" s="3">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
@@ -3055,27 +3034,27 @@
         <v>129</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="J26" s="3">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>132</v>
@@ -3090,7 +3069,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -3098,60 +3077,60 @@
         <v>134</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="J29" s="3">
         <v>13</v>
@@ -3159,147 +3138,147 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="J30" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="J32" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>153</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J33" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>158</v>
@@ -3311,24 +3290,24 @@
         <v>159</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="J34" s="3">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>38</v>
@@ -3346,7 +3325,7 @@
         <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -3357,7 +3336,7 @@
         <v>165</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>59</v>
@@ -3366,102 +3345,104 @@
         <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="J37" s="3">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J38" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>24</v>
       </c>
@@ -3469,10 +3450,10 @@
         <v>178</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J39" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
@@ -3480,61 +3461,59 @@
         <v>179</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="J40" s="3">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>184</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="J41" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -3551,31 +3530,33 @@
         <v>59</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="G42" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="J42" s="3">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>59</v>
@@ -3588,27 +3569,27 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>68</v>
@@ -3621,21 +3602,21 @@
         <v>196</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>59</v>
@@ -3651,21 +3632,21 @@
         <v>199</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>59</v>
@@ -3684,51 +3665,51 @@
         <v>203</v>
       </c>
       <c r="J46" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>68</v>
@@ -3738,27 +3719,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>68</v>
@@ -3768,27 +3749,27 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>68</v>
@@ -3798,27 +3779,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>68</v>
@@ -3828,114 +3809,114 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>210</v>
+        <v>59</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J52" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="J53" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>233</v>
+        <v>134</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>59</v>
@@ -3948,10 +3929,10 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="J55" s="3">
         <v>1</v>
@@ -3959,16 +3940,16 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>68</v>
@@ -3978,27 +3959,27 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>68</v>
@@ -4008,10 +3989,10 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="J57" s="3">
         <v>1</v>
@@ -4019,46 +4000,46 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>245</v>
+        <v>62</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="J58" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>249</v>
+        <v>134</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>68</v>
@@ -4068,54 +4049,56 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>59</v>
@@ -4123,64 +4106,62 @@
       <c r="E61" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>257</v>
-      </c>
+      <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>62</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="J62" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>68</v>
@@ -4190,117 +4171,121 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="J63" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F64" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>130</v>
+        <v>256</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J65" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="J66" s="3">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>68</v>
@@ -4310,84 +4295,84 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="J67" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>56</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="J68" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>66</v>
+        <v>270</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>59</v>
@@ -4395,63 +4380,59 @@
       <c r="E70" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>257</v>
-      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>284</v>
+        <v>106</v>
       </c>
       <c r="J70" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>285</v>
+        <v>95</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>286</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>130</v>
+        <v>275</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>289</v>
+        <v>192</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>59</v>
@@ -4464,24 +4445,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>231</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>59</v>
@@ -4494,24 +4475,24 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>293</v>
+        <v>233</v>
       </c>
       <c r="J73" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>56</v>
+        <v>279</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>59</v>
@@ -4524,27 +4505,27 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>68</v>
@@ -4554,54 +4535,54 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>59</v>
@@ -4614,24 +4595,24 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="J77" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>59</v>
@@ -4644,54 +4625,54 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="J78" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="J79" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>59</v>
@@ -4704,54 +4685,54 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="J80" s="3">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>310</v>
+        <v>134</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="J81" s="3">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>59</v>
@@ -4759,15 +4740,17 @@
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="J82" s="3">
         <v>0</v>
@@ -4775,76 +4758,76 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>315</v>
+        <v>56</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>44</v>
+        <v>220</v>
       </c>
       <c r="J83" s="3">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>130</v>
+        <v>306</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="J84" s="3">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>191</v>
+        <v>311</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>68</v>
@@ -4854,54 +4837,54 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>323</v>
+        <v>176</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>326</v>
+        <v>106</v>
       </c>
       <c r="J86" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>59</v>
@@ -4914,40 +4897,40 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="J87" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>62</v>
+        <v>318</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4955,13 +4938,13 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>331</v>
+        <v>62</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>332</v>
+        <v>201</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>59</v>
@@ -4974,27 +4957,27 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J89" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>68</v>
@@ -5004,57 +4987,57 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="J90" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>68</v>
@@ -5064,24 +5047,24 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="J92" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>341</v>
+        <v>134</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>59</v>
@@ -5094,57 +5077,59 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>229</v>
+        <v>65</v>
       </c>
       <c r="J93" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>336</v>
+      </c>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="J94" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>68</v>
@@ -5154,27 +5139,27 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>102</v>
+        <v>292</v>
       </c>
       <c r="J95" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>245</v>
+        <v>342</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>351</v>
+        <v>192</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>68</v>
@@ -5184,54 +5169,54 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="J97" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>59</v>
@@ -5244,57 +5229,57 @@
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>151</v>
+        <v>313</v>
       </c>
       <c r="J99" s="3">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>191</v>
+        <v>353</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>38</v>
@@ -5304,10 +5289,10 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5315,13 +5300,13 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>59</v>
@@ -5334,27 +5319,27 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="J101" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>339</v>
+        <v>223</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>68</v>
@@ -5364,27 +5349,27 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="J102" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>130</v>
+        <v>342</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>270</v>
+        <v>361</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>68</v>
@@ -5394,10 +5379,10 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="J103" s="3">
         <v>0</v>
@@ -5405,19 +5390,19 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>62</v>
+        <v>363</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>270</v>
+        <v>365</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>366</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
@@ -5427,10 +5412,10 @@
         <v>367</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>193</v>
+        <v>292</v>
       </c>
       <c r="J104" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105">
@@ -5438,16 +5423,16 @@
         <v>368</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>311</v>
+        <v>210</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
@@ -5457,24 +5442,24 @@
         <v>369</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="J105" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>371</v>
-      </c>
       <c r="C106" s="3" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>68</v>
@@ -5484,40 +5469,40 @@
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="J106" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="J107" s="3">
         <v>0</v>
@@ -5525,46 +5510,46 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>205</v>
+        <v>364</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>191</v>
+        <v>365</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>68</v>
+        <v>366</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>102</v>
+        <v>233</v>
       </c>
       <c r="J108" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="D109" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>68</v>
@@ -5574,10 +5559,10 @@
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="J109" s="3">
         <v>0</v>
@@ -5585,13 +5570,13 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>381</v>
-      </c>
       <c r="C110" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>59</v>
@@ -5604,87 +5589,87 @@
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J110" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>214</v>
+        <v>382</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="J111" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>263</v>
+        <v>364</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>387</v>
+        <v>68</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="J112" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>38</v>
@@ -5694,27 +5679,27 @@
         <v>23</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="J113" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C114" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="D114" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>68</v>
@@ -5727,7 +5712,7 @@
         <v>394</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>229</v>
+        <v>106</v>
       </c>
       <c r="J114" s="3">
         <v>5</v>
@@ -5735,46 +5720,46 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="J115" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>398</v>
+        <v>192</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>68</v>
@@ -5784,24 +5769,24 @@
         <v>23</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>102</v>
+        <v>401</v>
       </c>
       <c r="J116" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>400</v>
+        <v>176</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>59</v>
@@ -5814,57 +5799,57 @@
         <v>23</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="J117" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>403</v>
+        <v>134</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C118" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="D118" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="J118" s="3">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>407</v>
-      </c>
       <c r="C119" s="3" t="s">
-        <v>408</v>
+        <v>192</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>68</v>
@@ -5874,107 +5859,47 @@
         <v>23</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>326</v>
+        <v>106</v>
       </c>
       <c r="J119" s="3">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>172</v>
+        <v>408</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>229</v>
+        <v>160</v>
       </c>
       <c r="J120" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J121" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J122" s="3">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J122"/>
+  <autoFilter ref="A1:J120"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6095,8 +6020,6 @@
     <hyperlink ref="H118" r:id="rId117"/>
     <hyperlink ref="H119" r:id="rId118"/>
     <hyperlink ref="H120" r:id="rId119"/>
-    <hyperlink ref="H121" r:id="rId120"/>
-    <hyperlink ref="H122" r:id="rId121"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6104,9 +6027,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6138,13 +6061,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6152,18 +6075,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6171,18 +6094,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6190,18 +6113,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>130</v>
+        <v>221</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6209,18 +6132,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6228,18 +6151,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6247,18 +6170,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>300</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6266,18 +6189,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>255</v>
+        <v>318</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>256</v>
+        <v>319</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6285,18 +6208,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>258</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6304,18 +6227,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>334</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>289</v>
+        <v>207</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6323,18 +6246,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>56</v>
+        <v>351</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>191</v>
+        <v>353</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6342,18 +6265,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>299</v>
+        <v>356</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6361,18 +6284,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>300</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>191</v>
+        <v>361</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6380,18 +6303,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>321</v>
+        <v>210</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6399,18 +6322,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>62</v>
+        <v>351</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6418,18 +6341,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>330</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>172</v>
+        <v>376</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>336</v>
+        <v>218</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>270</v>
+        <v>377</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6437,18 +6360,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>245</v>
+        <v>379</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>351</v>
+        <v>229</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -6456,18 +6379,18 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>342</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>270</v>
+        <v>384</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -6475,18 +6398,18 @@
         <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>191</v>
+        <v>388</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -6494,106 +6417,11 @@
         <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G20"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6614,11 +6442,6 @@
     <hyperlink ref="G18" r:id="rId17"/>
     <hyperlink ref="G19" r:id="rId18"/>
     <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
-    <hyperlink ref="G24" r:id="rId23"/>
-    <hyperlink ref="G25" r:id="rId24"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6632,15 +6455,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B2" s="3">
         <v>31</v>
@@ -6648,63 +6471,63 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>423</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>416</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
@@ -6712,7 +6535,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -6720,31 +6543,31 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B12" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6752,7 +6575,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -6765,7 +6588,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6774,7 +6597,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
@@ -6787,7 +6610,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6795,15 +6618,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6811,10 +6634,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -6827,7 +6650,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6835,7 +6658,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -6843,15 +6666,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>311</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6859,7 +6682,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6867,7 +6690,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6875,7 +6698,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6883,7 +6706,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6891,7 +6714,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6912,16 +6735,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2">
@@ -6929,13 +6752,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3">
-        <v>19.2</v>
+        <v>22.7</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -6943,13 +6766,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3">
-        <v>17.3</v>
+        <v>19.2</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6957,7 +6780,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
         <v>17.3</v>
@@ -6971,13 +6794,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="C5" s="3">
-        <v>14.7</v>
+        <v>17.3</v>
       </c>
       <c r="D5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -6999,7 +6822,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C7" s="3">
         <v>10.1</v>
@@ -7013,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C8" s="3">
         <v>7.3</v>
@@ -7041,13 +6864,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>119</v>
+        <v>218</v>
       </c>
       <c r="C10" s="3">
-        <v>6.2</v>
+        <v>7.0</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -7055,13 +6878,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="C11" s="3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="D11" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -7069,10 +6892,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="C12" s="3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -7083,13 +6906,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
       <c r="C13" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -7097,7 +6920,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -7111,7 +6934,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>205</v>
+        <v>370</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -7125,13 +6948,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>246</v>
+        <v>165</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7151,18 +6974,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -7173,10 +6996,10 @@
         <v>68</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4">
@@ -7184,10 +7007,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -7206,7 +7029,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2">
@@ -7214,15 +7037,15 @@
         <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -7235,41 +7058,33 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>389</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -7282,7 +7097,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -7294,10 +7109,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7309,10 +7124,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -7329,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>77</v>
@@ -7338,19 +7153,19 @@
         <v>78</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7361,31 +7176,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>248</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -7393,31 +7208,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>217</v>
+        <v>445</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F4" s="3">
+        <v>83</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="F4" s="3">
-        <v>92</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
@@ -7425,31 +7240,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>457</v>
+        <v>192</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>102</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6">
@@ -7457,31 +7272,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>465</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -7489,31 +7304,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>191</v>
+        <v>460</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="F7" s="3">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
@@ -7521,31 +7336,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F8" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -7553,31 +7368,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="F9" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>248</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -7585,31 +7400,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>480</v>
+        <v>169</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F10" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -7617,31 +7432,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>165</v>
+        <v>475</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12">
@@ -7649,31 +7464,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>465</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -7681,31 +7496,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>489</v>
+        <v>192</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -7713,31 +7528,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -7745,31 +7560,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>44</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16">
@@ -7777,31 +7592,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>270</v>
+        <v>493</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17">
@@ -7809,31 +7624,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>503</v>
+        <v>469</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>191</v>
+        <v>361</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -7841,31 +7656,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="F18" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19">
@@ -7873,31 +7688,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>119</v>
+        <v>370</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>512</v>
+        <v>207</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>197</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20">
@@ -7905,31 +7720,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>479</v>
+        <v>508</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>516</v>
+        <v>229</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F20" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>519</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -7937,31 +7752,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>191</v>
+        <v>353</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>156</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W25.xlsx
+++ b/reports/devops-jobs-israel-2026-W25.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-16T11:29:24</t>
+    <t xml:space="preserve">2026-06-17T11:13:12</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7%</t>
+    <t xml:space="preserve">0.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -159,1416 +159,1374 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
   </si>
   <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888541101?gh_jid=4888541101</t>
   </si>
   <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7818160&amp;gh_jid=7818160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of AI Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Services DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Austin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin, Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Boston)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, Massachusetts, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (New York)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010964004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Rhode Island)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providence, Rhode Island, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010965004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (Washington)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finubit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-finubit-4428632503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; IT Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contguard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4428872095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4428419944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36609)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36609-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428812089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-STAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-g-stat-4427413680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aqua-security-4418683555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-bagira-4429912421</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Tech Lead</t>
   </si>
   <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Python, Prometheus, Grafana, Pulumi, Networking, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7911982?gh_jid=7911982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Prometheus, Grafana, ELK/Elastic, Pulumi, CloudFormation, Kafka, Networking, Security, Argo CD, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7894294?gh_jid=7894294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7818160&amp;gh_jid=7818160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of AI Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7625966&amp;gh_jid=7625966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Austin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austin, Texas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Boston)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston, Massachusetts, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (New York)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010964004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Rhode Island)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providence, Rhode Island, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010965004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Washington)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washington, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finubit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-finubit-4428632503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4428872095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36609)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36609-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428812089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4426065244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-compie-technologies-4428808414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4425723456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4427304910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XM Cyber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz (part of Google Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-part-of-google-cloud-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Azure Platform &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-platform-devops-engineer-at-gini-apps-4428816993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-part-of-google-cloud-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4378744789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Semiconductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4427729203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4425749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team8 Stealth Mode Startup-Senior Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team8-stealth-mode-startup-senior-infra-engineer-at-team8-4427476799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psistar (Maverick AI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-infrastructure-engineer-at-psistar-maverick-ai-4426497175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-iai-israel-aerospace-industries-4412802073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Squad Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group (Copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-copy-at-bigpanda-4427444455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4425771367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIGO Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
   </si>
   <si>
     <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4425737474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-global-e-4425722658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4425736215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-STAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-g-stat-4427413680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-compie-technologies-4428808414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25078)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4425723456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-coralogix-4368406182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infotree Global Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-infotree-global-solutions-4418256545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4425760569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-bigbrain-at-monday-com-4428621761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-quanthealth-4425994726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group (Copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-copy-at-bigpanda-4427444455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-quantum-machines-4412371822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentee Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-mentee-robotics-4422793922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aman Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aman-group-4423678087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer | AWS | Kubernetes | Hybrid | Tel Aviv Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T&amp;S Talents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-aws-kubernetes-hybrid-tel-aviv-area-at-t-s-talents-4414893892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Software Engineer - SAP Cloud Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-software-engineer-sap-cloud-virtualization-at-sap-4417871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bynet-data-communications-4423131095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4421593110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4427729203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpticSolution</t>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4408743594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer – Microsoft Infrastructure &amp; Cloud (Help Desk + 3rd Tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-MEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-%E2%80%93-microsoft-infrastructure-cloud-help-desk-%2B-3rd-tier-at-g-mel-4429114041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (36613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-opticsolution-4427439160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (36613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Extreme</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYL Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-dyl-group-4428654157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ML Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psistar (Maverick AI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-infrastructure-engineer-at-psistar-maverick-ai-4426497175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-extreme-4426777242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer - Electronic Warfare Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-electronic-warfare-systems-at-regulus-4427439098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Squad Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, NSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Hai, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-nsv-at-nvidia-4395479258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tikal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tikal-4425757948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIGO Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4425741384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1584,19 +1542,13 @@
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
+    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1748,7 +1700,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -1756,7 +1708,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1764,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1772,7 +1724,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>626</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10">
@@ -1780,7 +1732,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1844,7 +1796,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1804,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1871,36 +1823,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1908,7 +1860,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1927,47 +1879,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>521</v>
+        <v>406</v>
       </c>
       <c r="B6" s="3">
         <v>17</v>
@@ -1975,31 +1927,31 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>257</v>
+        <v>401</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>522</v>
+        <v>405</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>422</v>
+        <v>507</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>417</v>
+        <v>508</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -2007,7 +1959,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>523</v>
+        <v>276</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -2015,7 +1967,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -2023,34 +1975,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>525</v>
+        <v>402</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2075,13 +2027,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2">
@@ -2089,13 +2041,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2104,88 +2056,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3">
-        <v>36.9</v>
+        <v>32.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.4</v>
+        <v>9.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.4</v>
+        <v>32.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.8</v>
+        <v>18.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2197,7 +2149,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2269,7 +2221,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -2301,7 +2253,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -2330,15 +2282,15 @@
         <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -2353,24 +2305,24 @@
         <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
@@ -2385,7 +2337,7 @@
         <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
@@ -2394,15 +2346,15 @@
         <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>
@@ -2417,62 +2369,62 @@
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="J8" s="3">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>59</v>
@@ -2481,27 +2433,27 @@
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>59</v>
@@ -2510,33 +2462,33 @@
         <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>59</v>
@@ -2557,7 +2509,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -2565,95 +2517,95 @@
         <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J14" s="3">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -2661,124 +2613,124 @@
         <v>84</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J16" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J17" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J18" s="3">
         <v>6</v>
@@ -2786,10 +2738,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>59</v>
@@ -2813,15 +2765,15 @@
         <v>103</v>
       </c>
       <c r="J19" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>59</v>
@@ -2833,19 +2785,19 @@
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="J20" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2853,7 +2805,7 @@
         <v>107</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>59</v>
@@ -2874,21 +2826,21 @@
         <v>109</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J21" s="3">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>59</v>
@@ -2897,27 +2849,27 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="J22" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>59</v>
@@ -2926,33 +2878,33 @@
         <v>59</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="J23" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>59</v>
@@ -2961,167 +2913,167 @@
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="J24" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="J27" s="3">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="J28" s="3">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
@@ -3130,10 +3082,10 @@
         <v>142</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="J29" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -3141,19 +3093,19 @@
         <v>143</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>144</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
@@ -3162,10 +3114,10 @@
         <v>145</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="J30" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -3173,19 +3125,19 @@
         <v>146</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>147</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
@@ -3194,39 +3146,39 @@
         <v>148</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="J31" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="J32" s="3">
         <v>5</v>
@@ -3234,162 +3186,160 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>160</v>
+        <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="J35" s="3">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D36" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J36" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="J37" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
@@ -3397,16 +3347,16 @@
         <v>173</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>174</v>
@@ -3421,7 +3371,7 @@
         <v>41</v>
       </c>
       <c r="J38" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
@@ -3429,61 +3379,59 @@
         <v>176</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>177</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H40" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="J40" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -3491,78 +3439,78 @@
         <v>183</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="G41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="J41" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>188</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="J42" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3572,27 +3520,27 @@
         <v>193</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="D44" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -3602,367 +3550,367 @@
         <v>196</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J45" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>106</v>
+        <v>218</v>
       </c>
       <c r="J50" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="J52" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J56" s="3">
         <v>23</v>
@@ -3970,43 +3918,43 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>59</v>
@@ -4019,316 +3967,310 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>243</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>245</v>
+        <v>173</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>243</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="J64" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>257</v>
-      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>261</v>
+        <v>191</v>
       </c>
       <c r="J66" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>59</v>
+        <v>269</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="J68" s="3">
         <v>1</v>
@@ -4336,119 +4278,121 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F69" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>229</v>
+        <v>279</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="J71" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="J72" s="3">
         <v>22</v>
@@ -4456,103 +4400,103 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="J73" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>279</v>
+        <v>88</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>218</v>
+        <v>289</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="J74" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>98</v>
+        <v>238</v>
       </c>
       <c r="J75" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>59</v>
@@ -4565,84 +4509,84 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="J76" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>289</v>
+        <v>128</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>292</v>
+        <v>191</v>
       </c>
       <c r="J78" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>111</v>
+        <v>301</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>59</v>
@@ -4655,84 +4599,86 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>295</v>
+        <v>104</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="J80" s="3">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="J81" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>300</v>
+        <v>64</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>301</v>
+        <v>203</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>59</v>
@@ -4740,197 +4686,195 @@
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>302</v>
-      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="J83" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J85" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>176</v>
+        <v>319</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J86" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>250</v>
+        <v>128</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>192</v>
+        <v>323</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="J87" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4938,13 +4882,13 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>201</v>
+        <v>329</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>59</v>
@@ -4957,10 +4901,10 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
@@ -4968,318 +4912,318 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>324</v>
+        <v>189</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J90" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>134</v>
+        <v>334</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>327</v>
+        <v>189</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F91" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>336</v>
+      </c>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="J91" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>330</v>
+        <v>233</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E93" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="J93" s="3">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>336</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="J95" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>106</v>
+        <v>205</v>
       </c>
       <c r="J96" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>62</v>
+        <v>350</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>59</v>
+        <v>222</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="J97" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>134</v>
+        <v>350</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="J98" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>218</v>
+        <v>356</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>313</v>
+        <v>191</v>
       </c>
       <c r="J99" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>353</v>
+        <v>189</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>38</v>
@@ -5289,40 +5233,40 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>356</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>229</v>
+        <v>357</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -5330,29 +5274,29 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>224</v>
+        <v>59</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="J102" s="3">
         <v>1</v>
@@ -5360,89 +5304,89 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J103" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>366</v>
+        <v>38</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>292</v>
+        <v>202</v>
       </c>
       <c r="J104" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>210</v>
+        <v>374</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>207</v>
+        <v>316</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J105" s="3">
         <v>0</v>
@@ -5450,43 +5394,43 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="J106" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>59</v>
@@ -5499,117 +5443,117 @@
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>365</v>
+        <v>233</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>366</v>
+        <v>60</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="J108" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="J109" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="J110" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>351</v>
+        <v>391</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>382</v>
+        <v>189</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>38</v>
@@ -5619,287 +5563,17 @@
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="J111" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J112" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J113" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J114" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J115" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="J116" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J117" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J118" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J119" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J120" s="3">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J120"/>
+  <autoFilter ref="A1:J111"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6011,15 +5685,6 @@
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
-    <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
-    <hyperlink ref="H115" r:id="rId114"/>
-    <hyperlink ref="H116" r:id="rId115"/>
-    <hyperlink ref="H117" r:id="rId116"/>
-    <hyperlink ref="H118" r:id="rId117"/>
-    <hyperlink ref="H119" r:id="rId118"/>
-    <hyperlink ref="H120" r:id="rId119"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6028,8 +5693,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6061,13 +5726,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>134</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6075,18 +5740,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6094,18 +5759,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6113,18 +5778,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6132,18 +5797,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6151,18 +5816,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6170,18 +5835,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6189,18 +5854,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6208,18 +5873,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>306</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6227,18 +5892,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>207</v>
+        <v>327</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6246,18 +5911,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>351</v>
+        <v>45</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>353</v>
+        <v>195</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6265,18 +5930,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>356</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>229</v>
+        <v>357</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6284,18 +5949,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6303,18 +5968,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>210</v>
+        <v>374</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>207</v>
+        <v>316</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6322,18 +5987,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6341,18 +6006,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>218</v>
+        <v>392</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>377</v>
+        <v>189</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6360,68 +6025,11 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G17"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6439,9 +6047,6 @@
     <hyperlink ref="G15" r:id="rId14"/>
     <hyperlink ref="G16" r:id="rId15"/>
     <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6455,87 +6060,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>243</v>
+        <v>336</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>399</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -6543,23 +6148,23 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -6567,7 +6172,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6575,10 +6180,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6588,7 +6193,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6597,7 +6202,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2">
@@ -6610,7 +6215,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6618,7 +6223,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6626,7 +6231,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6634,15 +6239,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="B6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6650,23 +6255,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>364</v>
+        <v>150</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6674,7 +6279,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6682,7 +6287,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6690,7 +6295,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>180</v>
+        <v>262</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6698,7 +6303,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6706,7 +6311,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>210</v>
+        <v>289</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6714,7 +6319,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6728,23 +6333,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2">
@@ -6752,7 +6357,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3">
         <v>22.7</v>
@@ -6766,13 +6371,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="D3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -6780,13 +6385,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C4" s="3">
-        <v>17.3</v>
+        <v>19.2</v>
       </c>
       <c r="D4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -6794,7 +6399,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C5" s="3">
         <v>17.3</v>
@@ -6808,13 +6413,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="C6" s="3">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -6822,10 +6427,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
@@ -6836,7 +6441,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C8" s="3">
         <v>7.3</v>
@@ -6850,10 +6455,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3">
-        <v>7.0</v>
+        <v>6.2</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6864,13 +6469,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="C10" s="3">
-        <v>7.0</v>
+        <v>2.8</v>
       </c>
       <c r="D10" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6878,10 +6483,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="C11" s="3">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -6892,13 +6497,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>364</v>
+        <v>212</v>
       </c>
       <c r="C12" s="3">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6906,7 +6511,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>180</v>
+        <v>262</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6920,13 +6525,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6934,10 +6539,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>370</v>
+        <v>275</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6948,13 +6553,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>165</v>
+        <v>289</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6974,18 +6579,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>287</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6993,13 +6598,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4">
@@ -7007,10 +6612,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -7029,7 +6634,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
@@ -7037,15 +6642,15 @@
         <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -7053,20 +6658,20 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -7074,17 +6679,25 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>131</v>
+        <v>222</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>389</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -7097,7 +6710,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -7109,10 +6722,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7124,10 +6737,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -7144,28 +6757,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7176,31 +6789,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>223</v>
+        <v>424</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F3" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
@@ -7208,31 +6821,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>445</v>
+        <v>221</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="F4" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
@@ -7240,31 +6853,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>450</v>
+        <v>383</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>192</v>
+        <v>327</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F5" s="3">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>453</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
@@ -7272,31 +6885,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7">
@@ -7304,31 +6917,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>460</v>
+        <v>189</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>233</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -7336,31 +6949,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>466</v>
+        <v>433</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -7368,31 +6981,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F9" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>200</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -7400,28 +7013,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7432,31 +7045,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>475</v>
+        <v>239</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>453</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -7464,31 +7077,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>160</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13">
@@ -7496,31 +7109,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>192</v>
+        <v>345</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
@@ -7528,31 +7141,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -7560,31 +7173,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>489</v>
+        <v>225</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="F15" s="3">
         <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>313</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">
@@ -7592,31 +7205,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>475</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>493</v>
+        <v>233</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>496</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17">
@@ -7624,31 +7237,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>497</v>
+        <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>361</v>
+        <v>479</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F17" s="3">
         <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18">
@@ -7656,31 +7269,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>229</v>
+        <v>485</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F18" s="3">
         <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>194</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19">
@@ -7688,31 +7301,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>370</v>
+        <v>490</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="F19" s="3">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>401</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20">
@@ -7720,31 +7333,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>71</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
@@ -7752,31 +7365,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F21" s="3">
         <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W25.xlsx
+++ b/reports/devops-jobs-israel-2026-W25.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="547">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-17T11:13:12</t>
+    <t xml:space="preserve">2026-06-18T10:43:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9%</t>
+    <t xml:space="preserve">2.4%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -351,15 +351,27 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Ansible, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Observability</t>
   </si>
   <si>
@@ -531,250 +543,754 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finubit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-finubit-4428632503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4430430529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; IT Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contguard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Yokneam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-yokneam-at-codevalue-4429938053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36609)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36609-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428812089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-gotfriends-4426809078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; AI Platform team lead - JB-680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-platform-team-lead-jb-680-at-pwc-next-technology-solutions-4428686942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; CloudOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-at-moveo-source-4427499835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4430162880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tools &amp; Automation Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integra LifeSciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tools-automation-specialist-at-integra-lifesciences-4377406238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4427444455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-global-e-4425722658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4430427880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-hyro-4418385319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XM Cyber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finubit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-finubit-4428632503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; IT Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contguard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4428872095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4428419944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36609)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36609-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428812089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-compie-technologies-4428808414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4427304910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4429038091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teva Pharmaceuticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-unity-4428813920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Semiconductor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4427729203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4425749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psistar (Maverick AI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-infrastructure-engineer-at-psistar-maverick-ai-4426497175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (533457)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-533457-at-malamteam-4429959988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpticSolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-opticsolution-4427439160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/navigation-system-engineer-at-iai-israel-aerospace-industries-4425771548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-optimum-4429902504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYL Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-dyl-group-4428654157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Fend Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Squad Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nayax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4428817819</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Manager</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-STAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-g-stat-4427413680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25078)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-bagira-4429912421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team8 Stealth Mode Startup-Senior Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team8-stealth-mode-startup-senior-infra-engineer-at-team8-4427476799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
   </si>
   <si>
     <t xml:space="preserve">Aqua Security</t>
@@ -783,643 +1299,244 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aqua-security-4418683555</t>
   </si>
   <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-bagira-4429912421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-compie-technologies-4428808414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-logica-it-4425723456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4427304910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XM Cyber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz (part of Google Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-part-of-google-cloud-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Azure Platform &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-platform-devops-engineer-at-gini-apps-4428816993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-part-of-google-cloud-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4427156928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4378744789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4427729203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4427054576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4425749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8 Stealth Mode Startup-Senior Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team8-stealth-mode-startup-senior-infra-engineer-at-team8-4427476799</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-nvidia-4395473391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
   </si>
   <si>
-    <t xml:space="preserve">ML Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psistar (Maverick AI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-infrastructure-engineer-at-psistar-maverick-ai-4426497175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-iai-israel-aerospace-industries-4412802073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Squad Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group (Copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-copy-at-bigpanda-4427444455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud DevOps Team Leader 229534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-team-leader-229534-at-experis-israel-4425771367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (U.S Citizen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIGO Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-u-s-citizen-at-oligo-security-4427007687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4408743594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer – Microsoft Infrastructure &amp; Cloud (Help Desk + 3rd Tier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-MEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-%E2%80%93-microsoft-infrastructure-cloud-help-desk-%2B-3rd-tier-at-g-mel-4429114041</t>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
     <t xml:space="preserve">AI Operations Engineer</t>
@@ -1443,9 +1560,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
     <t xml:space="preserve">Menora Mivtachim Group</t>
   </si>
   <si>
@@ -1455,6 +1569,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
   </si>
   <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">Helpdesk Specialist</t>
   </si>
   <si>
@@ -1467,18 +1590,12 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
     <t xml:space="preserve">Innoviz Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -1488,42 +1605,6 @@
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -1539,16 +1620,19 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1700,7 +1784,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
@@ -1708,7 +1792,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1716,7 +1800,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -1724,7 +1808,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>642</v>
+        <v>662</v>
       </c>
     </row>
     <row r="10">
@@ -1732,7 +1816,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1796,7 +1880,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -1823,36 +1907,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1860,7 +1944,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1879,111 +1963,111 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>503</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>506</v>
+        <v>441</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>406</v>
+        <v>533</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>405</v>
+        <v>534</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>508</v>
+        <v>346</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>397</v>
+        <v>537</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
@@ -1991,18 +2075,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2027,13 +2111,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
@@ -2044,10 +2128,10 @@
         <v>42</v>
       </c>
       <c r="C2" s="3">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2056,88 +2140,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3">
-        <v>32.9</v>
+        <v>55.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.2</v>
+        <v>7.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.0</v>
+        <v>3.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.8</v>
+        <v>35.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>18.0</v>
+        <v>14.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2221,7 +2305,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -2253,7 +2337,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -2285,7 +2369,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -2317,7 +2401,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -2349,7 +2433,7 @@
         <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2381,7 +2465,7 @@
         <v>54</v>
       </c>
       <c r="J7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2413,7 +2497,7 @@
         <v>63</v>
       </c>
       <c r="J8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -2445,7 +2529,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -2477,7 +2561,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -2509,7 +2593,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -2541,7 +2625,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -2573,7 +2657,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -2605,7 +2689,7 @@
         <v>83</v>
       </c>
       <c r="J14" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -2637,7 +2721,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -2669,7 +2753,7 @@
         <v>91</v>
       </c>
       <c r="J16" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2701,7 +2785,7 @@
         <v>96</v>
       </c>
       <c r="J17" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2733,7 +2817,7 @@
         <v>99</v>
       </c>
       <c r="J18" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2765,7 +2849,7 @@
         <v>103</v>
       </c>
       <c r="J19" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -2797,7 +2881,7 @@
         <v>96</v>
       </c>
       <c r="J20" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2829,7 +2913,7 @@
         <v>44</v>
       </c>
       <c r="J21" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -2861,7 +2945,7 @@
         <v>115</v>
       </c>
       <c r="J22" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2869,48 +2953,48 @@
         <v>116</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J23" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>122</v>
@@ -2922,24 +3006,24 @@
         <v>123</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="J24" s="3">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
@@ -2954,27 +3038,27 @@
         <v>127</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="J25" s="3">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>130</v>
@@ -2989,7 +3073,7 @@
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -2997,60 +3081,60 @@
         <v>132</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="J28" s="3">
         <v>15</v>
@@ -3058,147 +3142,147 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="J29" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J30" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="J31" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>151</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J32" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>156</v>
@@ -3210,24 +3294,24 @@
         <v>157</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="J33" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>38</v>
@@ -3245,7 +3329,7 @@
         <v>41</v>
       </c>
       <c r="J34" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
@@ -3256,7 +3340,7 @@
         <v>163</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>59</v>
@@ -3265,62 +3349,62 @@
         <v>38</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="J35" s="3">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="C36" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="J36" s="3">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>59</v>
@@ -3328,29 +3412,31 @@
       <c r="E37" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="J37" s="3">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>59</v>
@@ -3359,33 +3445,33 @@
         <v>38</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J38" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>60</v>
@@ -3395,27 +3481,27 @@
         <v>24</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J39" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
@@ -3425,21 +3511,21 @@
         <v>24</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J40" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>59</v>
@@ -3451,30 +3537,30 @@
         <v>38</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>103</v>
       </c>
       <c r="J41" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>59</v>
@@ -3487,27 +3573,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>60</v>
@@ -3517,27 +3603,27 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>60</v>
@@ -3547,27 +3633,27 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="J44" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>60</v>
@@ -3580,21 +3666,21 @@
         <v>201</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>59</v>
@@ -3613,21 +3699,21 @@
         <v>205</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>60</v>
@@ -3637,10 +3723,10 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J47" s="3">
         <v>1</v>
@@ -3648,16 +3734,16 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>128</v>
+        <v>211</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>60</v>
@@ -3667,40 +3753,40 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>211</v>
+        <v>132</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="J49" s="3">
         <v>2</v>
@@ -3708,16 +3794,16 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>60</v>
@@ -3727,27 +3813,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="J50" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>222</v>
+        <v>59</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>60</v>
@@ -3757,27 +3843,27 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>60</v>
@@ -3787,10 +3873,10 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="J52" s="3">
         <v>2</v>
@@ -3798,49 +3884,49 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="J53" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
@@ -3850,21 +3936,21 @@
         <v>234</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>59</v>
@@ -3880,21 +3966,21 @@
         <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="J55" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>59</v>
@@ -3910,24 +3996,24 @@
         <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>241</v>
+        <v>115</v>
       </c>
       <c r="J56" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>60</v>
@@ -3940,21 +4026,21 @@
         <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="J57" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>59</v>
@@ -3970,24 +4056,24 @@
         <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>59</v>
+        <v>249</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>60</v>
@@ -3997,54 +4083,54 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>249</v>
+        <v>64</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>59</v>
@@ -4057,10 +4143,10 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="J61" s="3">
         <v>2</v>
@@ -4068,16 +4154,16 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>242</v>
+        <v>132</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>60</v>
@@ -4090,279 +4176,279 @@
         <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="J63" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>128</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F64" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>64</v>
+        <v>266</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>195</v>
+        <v>268</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>59</v>
+        <v>249</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>268</v>
+        <v>190</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>269</v>
+        <v>59</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>128</v>
+        <v>273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>59</v>
+        <v>276</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>134</v>
+        <v>198</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>276</v>
-      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="J69" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>235</v>
+        <v>64</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>278</v>
+        <v>212</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="J71" s="3">
         <v>0</v>
@@ -4370,73 +4456,73 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="J72" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>88</v>
+        <v>292</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>59</v>
@@ -4449,24 +4535,24 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="J74" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>59</v>
@@ -4479,84 +4565,84 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="J75" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>294</v>
+        <v>88</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="J76" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>289</v>
+        <v>193</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="J77" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>128</v>
+        <v>302</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>59</v>
@@ -4569,54 +4655,54 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>301</v>
+        <v>132</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="J79" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>104</v>
+        <v>306</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>59</v>
@@ -4629,24 +4715,24 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>306</v>
+        <v>104</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>59</v>
@@ -4654,31 +4740,29 @@
       <c r="E81" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>276</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>64</v>
+        <v>311</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>203</v>
+        <v>312</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>59</v>
@@ -4686,59 +4770,61 @@
       <c r="E82" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>238</v>
+        <v>44</v>
       </c>
       <c r="J83" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>312</v>
+        <v>274</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>59</v>
@@ -4751,54 +4837,54 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>44</v>
+        <v>319</v>
       </c>
       <c r="J84" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>314</v>
+        <v>64</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>316</v>
+        <v>203</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="J85" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>59</v>
@@ -4811,27 +4897,27 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="J86" s="3">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>323</v>
+        <v>248</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>59</v>
+        <v>249</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>60</v>
@@ -4841,27 +4927,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>191</v>
+        <v>327</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>60</v>
@@ -4871,54 +4957,54 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>195</v>
+        <v>281</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>331</v>
+        <v>64</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>59</v>
@@ -4931,89 +5017,87 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="J90" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>189</v>
+        <v>337</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>336</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>191</v>
+        <v>339</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="J92" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>128</v>
+        <v>341</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>60</v>
@@ -5023,70 +5107,72 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="J93" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>341</v>
+        <v>193</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F94" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>343</v>
+        <v>132</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>345</v>
+        <v>230</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J95" s="3">
         <v>1</v>
@@ -5094,29 +5180,29 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>347</v>
+        <v>45</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J96" s="3">
         <v>1</v>
@@ -5124,16 +5210,16 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>222</v>
+        <v>59</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>60</v>
@@ -5143,24 +5229,24 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="J97" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>59</v>
@@ -5168,59 +5254,63 @@
       <c r="E98" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="J98" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>357</v>
+        <v>190</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="J99" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>359</v>
+        <v>64</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>59</v>
@@ -5233,27 +5323,27 @@
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J100" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>357</v>
+        <v>230</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>60</v>
@@ -5263,24 +5353,24 @@
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>59</v>
@@ -5293,27 +5383,27 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="J102" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>367</v>
+        <v>193</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>368</v>
+        <v>213</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>60</v>
@@ -5323,87 +5413,87 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="J103" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>371</v>
+        <v>197</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>134</v>
+        <v>198</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="J104" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>316</v>
+        <v>376</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="J105" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>60</v>
@@ -5413,57 +5503,57 @@
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="J106" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="J107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>233</v>
+        <v>385</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>60</v>
@@ -5473,107 +5563,527 @@
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="J108" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>386</v>
+        <v>274</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>272</v>
+        <v>388</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>290</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>120</v>
+        <v>251</v>
       </c>
       <c r="J109" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="D110" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="J110" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>189</v>
+        <v>394</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="J111" s="3">
         <v>0</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J112" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J113" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J114" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J115" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J116" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J117" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J118" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J119" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J120" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J121" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J122" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J123" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J124" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J125" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J111"/>
+  <autoFilter ref="A1:J125"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5685,6 +6195,20 @@
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
     <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5694,7 +6218,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5726,32 +6250,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>198</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>219</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5759,18 +6283,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5778,18 +6302,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5797,18 +6321,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5816,18 +6340,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5835,18 +6359,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5854,18 +6378,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5873,18 +6397,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>306</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>307</v>
+        <v>212</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>189</v>
+        <v>281</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5892,18 +6416,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>325</v>
+        <v>64</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>327</v>
+        <v>190</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5911,18 +6435,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>45</v>
+        <v>341</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>195</v>
+        <v>343</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5930,18 +6454,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>356</v>
+        <v>193</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>357</v>
+        <v>213</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5949,18 +6473,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>371</v>
+        <v>190</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5968,18 +6492,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>316</v>
+        <v>197</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5987,18 +6511,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>233</v>
+        <v>394</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6006,18 +6530,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6025,11 +6549,87 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G21"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6047,6 +6647,10 @@
     <hyperlink ref="G15" r:id="rId14"/>
     <hyperlink ref="G16" r:id="rId15"/>
     <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6060,23 +6664,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="B3" s="3">
         <v>27</v>
@@ -6084,7 +6688,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="B4" s="3">
         <v>26</v>
@@ -6092,15 +6696,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="B6" s="3">
         <v>20</v>
@@ -6108,7 +6712,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B7" s="3">
         <v>19</v>
@@ -6116,7 +6720,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B8" s="3">
         <v>18</v>
@@ -6124,7 +6728,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
@@ -6132,15 +6736,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -6148,7 +6752,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="B12" s="3">
         <v>14</v>
@@ -6156,15 +6760,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>404</v>
+        <v>346</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -6172,7 +6776,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6180,7 +6784,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6193,7 +6797,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6202,20 +6806,20 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6223,7 +6827,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -6231,47 +6835,47 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>58</v>
+        <v>274</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6279,7 +6883,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6287,7 +6891,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6295,7 +6899,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>262</v>
+        <v>178</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6303,7 +6907,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>275</v>
+        <v>212</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6311,7 +6915,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>289</v>
+        <v>226</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6319,7 +6923,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>292</v>
+        <v>229</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6333,23 +6937,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>408</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
@@ -6399,7 +7003,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C5" s="3">
         <v>17.3</v>
@@ -6413,13 +7017,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3">
-        <v>13.4</v>
+        <v>10.9</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6427,13 +7031,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="C7" s="3">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -6441,13 +7045,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3">
-        <v>7.3</v>
+        <v>10.1</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6455,10 +7059,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="C9" s="3">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -6469,13 +7073,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="C10" s="3">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -6483,10 +7087,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -6497,10 +7101,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>212</v>
+        <v>111</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -6511,7 +7115,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>262</v>
+        <v>178</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6525,13 +7129,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6539,10 +7143,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6553,10 +7157,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="C16" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6579,18 +7183,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6601,10 +7205,10 @@
         <v>60</v>
       </c>
       <c r="B3" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>413</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4">
@@ -6612,10 +7216,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -6634,7 +7238,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2">
@@ -6642,15 +7246,15 @@
         <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6658,28 +7262,28 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6687,15 +7291,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>269</v>
+        <v>129</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6710,7 +7314,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6722,10 +7326,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>444</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6737,10 +7341,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>416</v>
+        <v>451</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>417</v>
+        <v>452</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6757,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>418</v>
+        <v>453</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>70</v>
@@ -6766,19 +7370,19 @@
         <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6789,31 +7393,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>422</v>
+        <v>457</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>424</v>
+        <v>281</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="F3" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -6821,31 +7425,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>428</v>
+        <v>372</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>429</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="F4" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
@@ -6853,31 +7457,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>383</v>
+        <v>466</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>327</v>
+        <v>190</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>99</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6">
@@ -6885,31 +7489,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>440</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -6917,31 +7521,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>189</v>
+        <v>281</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="F7" s="3">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -6949,31 +7553,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>446</v>
+        <v>375</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>189</v>
+        <v>376</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="F8" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -6981,31 +7585,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>450</v>
+        <v>167</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>272</v>
+        <v>168</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F9" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -7013,28 +7617,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>436</v>
+        <v>482</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>163</v>
+        <v>483</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>164</v>
+        <v>484</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>44</v>
@@ -7045,28 +7649,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="F11" s="3">
         <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>83</v>
@@ -7077,31 +7681,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F12" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>462</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -7109,31 +7713,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>345</v>
+        <v>230</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="F13" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -7141,31 +7745,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="F14" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>99</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15">
@@ -7173,31 +7777,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>225</v>
+        <v>503</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>205</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -7205,31 +7809,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="F16" s="3">
         <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>318</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -7237,31 +7841,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
+        <v>219</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>479</v>
+        <v>220</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="F17" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>482</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18">
@@ -7269,31 +7873,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>483</v>
+        <v>341</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>484</v>
+        <v>513</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>485</v>
+        <v>230</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="F18" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>488</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19">
@@ -7301,31 +7905,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>490</v>
+        <v>70</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>462</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20">
@@ -7333,31 +7937,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>494</v>
+        <v>121</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>221</v>
+        <v>520</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>205</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21">
@@ -7365,31 +7969,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>345</v>
+        <v>385</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W25.xlsx
+++ b/reports/devops-jobs-israel-2026-W25.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-18T10:43:03</t>
+    <t xml:space="preserve">2026-06-19T10:53:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4%</t>
+    <t xml:space="preserve">0.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -429,111 +429,63 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer (Austin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austin, Texas</t>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
   </si>
   <si>
     <t xml:space="preserve">Israel (other)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5710946004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Boston)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston, Massachusetts, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010968004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (New York)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010964004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Rhode Island)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providence, Rhode Island, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010965004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Washington)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washington, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6010969004</t>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Ansible, Helm, Prometheus, Istio, Kafka, Observability, Databricks, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8354571002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevSecOps</t>
   </si>
   <si>
@@ -585,22 +537,439 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; CloudOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-at-moveo-source-4427499835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4430439283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4430455192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; AI Platform team lead - JB-680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-platform-team-lead-jb-680-at-pwc-next-technology-solutions-4428686942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-gotfriends-4426809078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4430900015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4429090109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist (36628)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4430455329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XM Cyber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-unity-4428813920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Finubit</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-finubit-4428632503</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4427304910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4430430529</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
@@ -609,1030 +978,535 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
   </si>
   <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4430430529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; IT Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contguard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Engineer- Yokneam</t>
   </si>
   <si>
     <t xml:space="preserve">CodeValue</t>
   </si>
   <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-yokneam-at-codevalue-4429938053</t>
   </si>
   <si>
-    <t xml:space="preserve">amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36609)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36609-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428812089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planck</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
   </si>
   <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-gotfriends-4426809078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; AI Platform team lead - JB-680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-platform-team-lead-jb-680-at-pwc-next-technology-solutions-4428686942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; CloudOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-at-moveo-source-4427499835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4430162880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Azure DevOps &amp; Release Engineer</t>
+    <t xml:space="preserve">Senior Azure Platform &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-devops-release-engineer-at-abra-4426234726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tools &amp; Automation Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integra LifeSciences</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-platform-devops-engineer-at-gini-apps-4428816993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jeen-ai-4430489121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teva Pharmaceuticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team8 Stealth Mode Startup-Senior Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team8-stealth-mode-startup-senior-infra-engineer-at-team8-4427476799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4429038091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4429338126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYL Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-dyl-group-4428654157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4427444455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoTraffic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-notraffic-4430412124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAAT Delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-haat-delivery-4426484215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tools-automation-specialist-at-integra-lifesciences-4377406238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4427444455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-global-e-4425722658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-codevalue-4430427880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-hyro-4418385319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XM Cyber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-compie-technologies-4428808414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4427304910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4429038091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25078)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25078-at-yael-group-4423652623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps engineer - Data Security DevOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-data-security-devops-team-at-thales-4428647317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teva Pharmaceuticals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-unity-4428813920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Sub Contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Semiconductor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-sub-contractor-at-samsung-semiconductor-4428639232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4427729203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4425749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ML Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psistar (Maverick AI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-infrastructure-engineer-at-psistar-maverick-ai-4426497175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (533457)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-533457-at-malamteam-4429959988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpticSolution</t>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4425403074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer (36613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-opticsolution-4427439160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navigation System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/navigation-system-engineer-at-iai-israel-aerospace-industries-4425771548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-optimum-4429902504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYL Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-dyl-group-4428654157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-and-automation-engineer-at-nvidia-4395478350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-Fend Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Squad Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-squad-leader-at-milestone-systems-4427508430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nayax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4428817819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-bagira-4429912421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8 Stealth Mode Startup-Senior Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team8-stealth-mode-startup-senior-infra-engineer-at-team8-4427476799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aqua Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aqua-security-4418683555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-nvidia-4395473391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-ai-4427315937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (36613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1784,7 +1658,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
@@ -1792,7 +1666,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1800,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1808,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>662</v>
+        <v>678</v>
       </c>
     </row>
     <row r="10">
@@ -1816,7 +1690,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1880,7 +1754,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1888,7 +1762,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1907,36 +1781,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>446</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>528</v>
+        <v>420</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1944,7 +1818,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>529</v>
+        <v>487</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1963,119 +1837,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>530</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>531</v>
+        <v>489</v>
       </c>
       <c r="B2" s="3">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>532</v>
+        <v>490</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>437</v>
+        <v>392</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>534</v>
+        <v>493</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>535</v>
+        <v>299</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>262</v>
+        <v>494</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>536</v>
+        <v>495</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>537</v>
+        <v>388</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>433</v>
+        <v>389</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -2083,10 +1957,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>438</v>
+        <v>393</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2111,13 +1985,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>538</v>
+        <v>496</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>540</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2">
@@ -2125,13 +1999,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3">
-        <v>14.8</v>
+        <v>18.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2140,88 +2014,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3">
-        <v>55.9</v>
+        <v>38.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>542</v>
+        <v>500</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.8</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>543</v>
+        <v>501</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>544</v>
+        <v>502</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.3</v>
+        <v>35.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>545</v>
+        <v>503</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.0</v>
+        <v>18.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.4</v>
+        <v>16.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2233,7 +2107,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2305,7 +2179,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -2337,7 +2211,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -2369,7 +2243,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -2401,7 +2275,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -2433,7 +2307,7 @@
         <v>54</v>
       </c>
       <c r="J6" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2465,7 +2339,7 @@
         <v>54</v>
       </c>
       <c r="J7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2497,7 +2371,7 @@
         <v>63</v>
       </c>
       <c r="J8" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -2529,7 +2403,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -2561,7 +2435,7 @@
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -2593,7 +2467,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -2625,7 +2499,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -2657,7 +2531,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -2689,7 +2563,7 @@
         <v>83</v>
       </c>
       <c r="J14" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -2721,7 +2595,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -2753,7 +2627,7 @@
         <v>91</v>
       </c>
       <c r="J16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2785,7 +2659,7 @@
         <v>96</v>
       </c>
       <c r="J17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -2817,7 +2691,7 @@
         <v>99</v>
       </c>
       <c r="J18" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2849,7 +2723,7 @@
         <v>103</v>
       </c>
       <c r="J19" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -2881,7 +2755,7 @@
         <v>96</v>
       </c>
       <c r="J20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2913,7 +2787,7 @@
         <v>44</v>
       </c>
       <c r="J21" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
@@ -2945,7 +2819,7 @@
         <v>115</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2977,7 +2851,7 @@
         <v>119</v>
       </c>
       <c r="J23" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -3009,7 +2883,7 @@
         <v>124</v>
       </c>
       <c r="J24" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -3041,7 +2915,7 @@
         <v>103</v>
       </c>
       <c r="J25" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -3073,7 +2947,7 @@
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -3105,15 +2979,15 @@
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>137</v>
@@ -3134,245 +3008,241 @@
         <v>140</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="J28" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>138</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="J29" s="3">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="J31" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>151</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="J32" s="3">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J34" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="J35" s="3">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>59</v>
@@ -3381,140 +3251,136 @@
         <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="J36" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="J37" s="3">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="J38" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="J39" s="3">
         <v>24</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J39" s="3">
-        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J40" s="3">
         <v>14</v>
@@ -3522,48 +3388,46 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D41" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>186</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="J41" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>60</v>
@@ -3573,13 +3437,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J42" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3587,13 +3451,13 @@
         <v>132</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>60</v>
@@ -3603,13 +3467,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="J43" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -3617,13 +3481,13 @@
         <v>132</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>60</v>
@@ -3633,10 +3497,10 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -3647,10 +3511,10 @@
         <v>132</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>59</v>
@@ -3663,13 +3527,13 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3677,13 +3541,13 @@
         <v>132</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>60</v>
@@ -3693,24 +3557,24 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J46" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>138</v>
@@ -3723,30 +3587,30 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3759,37 +3623,37 @@
         <v>115</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3800,10 +3664,10 @@
         <v>219</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>60</v>
@@ -3813,24 +3677,24 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C51" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>59</v>
@@ -3843,13 +3707,13 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="J51" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3857,10 +3721,10 @@
         <v>132</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>59</v>
@@ -3873,30 +3737,30 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3906,7 +3770,7 @@
         <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="J53" s="3">
         <v>0</v>
@@ -3914,19 +3778,19 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
@@ -3936,7 +3800,7 @@
         <v>234</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="J54" s="3">
         <v>0</v>
@@ -3944,19 +3808,19 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3966,10 +3830,10 @@
         <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3980,10 +3844,10 @@
         <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>60</v>
@@ -3996,7 +3860,7 @@
         <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="J56" s="3">
         <v>0</v>
@@ -4004,43 +3868,43 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>59</v>
@@ -4053,10 +3917,10 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J58" s="3">
         <v>3</v>
@@ -4064,32 +3928,32 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>249</v>
+        <v>59</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="J59" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4097,10 +3961,10 @@
         <v>64</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>59</v>
@@ -4113,54 +3977,54 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>59</v>
@@ -4173,24 +4037,24 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="J62" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>258</v>
+        <v>132</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>59</v>
@@ -4203,56 +4067,54 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>132</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>262</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="J64" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>132</v>
+        <v>260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>59</v>
@@ -4265,70 +4127,70 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="J65" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>249</v>
+        <v>138</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>269</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="J67" s="3">
         <v>2</v>
@@ -4336,133 +4198,133 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>276</v>
+        <v>59</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="J68" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>278</v>
+        <v>88</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="J69" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>64</v>
+        <v>276</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>64</v>
+        <v>278</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>115</v>
+        <v>251</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>59</v>
@@ -4475,144 +4337,146 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>288</v>
+        <v>104</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>287</v>
+      </c>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="J74" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>64</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>225</v>
+        <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="J76" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>193</v>
+        <v>294</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>59</v>
@@ -4625,114 +4489,116 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>301</v>
+        <v>196</v>
       </c>
       <c r="J77" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>297</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>190</v>
+        <v>298</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F78" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>257</v>
+        <v>115</v>
       </c>
       <c r="J78" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>132</v>
+        <v>301</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="J80" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>104</v>
+        <v>307</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>59</v>
@@ -4745,42 +4611,40 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>311</v>
+        <v>132</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>312</v>
+        <v>216</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>313</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="J82" s="3">
         <v>2</v>
@@ -4788,46 +4652,46 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>64</v>
+        <v>311</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>44</v>
+        <v>314</v>
       </c>
       <c r="J83" s="3">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>317</v>
+        <v>132</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>60</v>
@@ -4837,57 +4701,57 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>319</v>
+        <v>115</v>
       </c>
       <c r="J84" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>203</v>
+        <v>317</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="J85" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>60</v>
@@ -4897,13 +4761,13 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="J86" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4911,13 +4775,13 @@
         <v>132</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>249</v>
+        <v>59</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>60</v>
@@ -4927,70 +4791,72 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>327</v>
+        <v>199</v>
       </c>
       <c r="J87" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>276</v>
+        <v>59</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F88" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="J89" s="3">
         <v>2</v>
@@ -4998,43 +4864,43 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>64</v>
+        <v>329</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="J90" s="3">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>335</v>
+        <v>132</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>337</v>
+        <v>210</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>138</v>
@@ -5047,57 +4913,57 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>339</v>
+        <v>202</v>
       </c>
       <c r="J91" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>229</v>
+        <v>334</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="J92" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>343</v>
+        <v>178</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>60</v>
@@ -5107,45 +4973,45 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J93" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>193</v>
+        <v>340</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>115</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5153,10 +5019,10 @@
         <v>132</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>59</v>
@@ -5169,27 +5035,27 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>45</v>
+        <v>345</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>203</v>
+        <v>347</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>38</v>
@@ -5199,27 +5065,27 @@
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>60</v>
@@ -5229,24 +5095,24 @@
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="J97" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>59</v>
@@ -5254,153 +5120,149 @@
       <c r="E98" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>357</v>
-      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="J98" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>360</v>
+        <v>297</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>190</v>
+        <v>298</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>357</v>
-      </c>
+      <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>64</v>
+        <v>349</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="J100" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>365</v>
+        <v>281</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="J101" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="J102" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>193</v>
+        <v>365</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>213</v>
+        <v>366</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>138</v>
@@ -5413,27 +5275,27 @@
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="J103" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>60</v>
@@ -5443,40 +5305,40 @@
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="J104" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>376</v>
+        <v>178</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J105" s="3">
         <v>3</v>
@@ -5484,13 +5346,13 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>379</v>
+        <v>222</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>59</v>
@@ -5503,587 +5365,137 @@
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="J106" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="J107" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>372</v>
+        <v>215</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>385</v>
+        <v>204</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="J108" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>274</v>
+        <v>380</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>388</v>
+        <v>258</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>251</v>
+        <v>124</v>
       </c>
       <c r="J109" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>390</v>
+        <v>64</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>274</v>
+        <v>382</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="J110" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J111" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J112" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J113" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="J114" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J115" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J116" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J117" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J118" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J119" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="I120" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J120" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J121" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="J122" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F123" s="3"/>
-      <c r="G123" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="I123" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J123" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="I124" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J124" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F125" s="3"/>
-      <c r="G125" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H125" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="I125" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J125" s="3">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J125"/>
+  <autoFilter ref="A1:J110"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -6194,21 +5606,6 @@
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
-    <hyperlink ref="H111" r:id="rId110"/>
-    <hyperlink ref="H112" r:id="rId111"/>
-    <hyperlink ref="H113" r:id="rId112"/>
-    <hyperlink ref="H114" r:id="rId113"/>
-    <hyperlink ref="H115" r:id="rId114"/>
-    <hyperlink ref="H116" r:id="rId115"/>
-    <hyperlink ref="H117" r:id="rId116"/>
-    <hyperlink ref="H118" r:id="rId117"/>
-    <hyperlink ref="H119" r:id="rId118"/>
-    <hyperlink ref="H120" r:id="rId119"/>
-    <hyperlink ref="H121" r:id="rId120"/>
-    <hyperlink ref="H122" r:id="rId121"/>
-    <hyperlink ref="H123" r:id="rId122"/>
-    <hyperlink ref="H124" r:id="rId123"/>
-    <hyperlink ref="H125" r:id="rId124"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6216,9 +5613,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6250,21 +5647,21 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
@@ -6272,10 +5669,10 @@
         <v>132</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -6283,18 +5680,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>132</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -6302,18 +5699,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>228</v>
+        <v>132</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -6321,18 +5718,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -6340,18 +5737,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>132</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6359,18 +5756,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -6378,18 +5775,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>266</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>268</v>
+        <v>178</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -6397,7 +5794,7 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -6405,10 +5802,10 @@
         <v>64</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -6416,18 +5813,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>64</v>
+        <v>301</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -6435,18 +5832,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>341</v>
+        <v>132</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>343</v>
+        <v>210</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -6454,18 +5851,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>193</v>
+        <v>353</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -6473,18 +5870,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -6492,18 +5889,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>382</v>
+        <v>222</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -6511,18 +5908,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>392</v>
+        <v>215</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>394</v>
+        <v>204</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6530,18 +5927,18 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>372</v>
+        <v>64</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>248</v>
+        <v>383</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -6549,87 +5946,11 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G17"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -6647,10 +5968,6 @@
     <hyperlink ref="G15" r:id="rId14"/>
     <hyperlink ref="G16" r:id="rId15"/>
     <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6664,130 +5981,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>431</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>433</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>434</v>
+        <v>389</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>435</v>
+        <v>325</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>436</v>
+        <v>391</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>437</v>
+        <v>299</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="B12" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>346</v>
+        <v>394</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>441</v>
+        <v>396</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6797,7 +6114,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6806,20 +6123,20 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>443</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6827,55 +6144,55 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="B6" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6883,7 +6200,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6891,7 +6208,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6899,7 +6216,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6907,7 +6224,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6915,7 +6232,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6923,7 +6240,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6937,23 +6254,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>443</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -7003,13 +6320,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="C5" s="3">
-        <v>17.3</v>
+        <v>10.9</v>
       </c>
       <c r="D5" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -7017,10 +6334,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="C6" s="3">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -7031,13 +6348,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="C7" s="3">
-        <v>10.8</v>
+        <v>7.3</v>
       </c>
       <c r="D7" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7045,13 +6362,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="C8" s="3">
-        <v>10.1</v>
+        <v>6.2</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7059,13 +6376,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>154</v>
+        <v>297</v>
       </c>
       <c r="C9" s="3">
-        <v>7.3</v>
+        <v>4.6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7073,13 +6390,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>274</v>
+        <v>111</v>
       </c>
       <c r="C10" s="3">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="D10" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -7087,13 +6404,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C11" s="3">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -7101,10 +6418,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="C12" s="3">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -7115,7 +6432,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -7129,7 +6446,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -7143,7 +6460,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C15" s="3">
         <v>2.8</v>
@@ -7157,13 +6474,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7183,18 +6500,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>447</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -7205,10 +6522,10 @@
         <v>60</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>448</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4">
@@ -7216,10 +6533,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>449</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -7238,7 +6555,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>446</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
@@ -7246,7 +6563,7 @@
         <v>59</v>
       </c>
       <c r="B2" s="3">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -7254,7 +6571,7 @@
         <v>138</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -7262,28 +6579,28 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -7291,15 +6608,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>129</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -7326,10 +6643,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -7341,10 +6658,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>451</v>
+        <v>406</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -7361,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>453</v>
+        <v>408</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>70</v>
@@ -7370,19 +6687,19 @@
         <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -7393,28 +6710,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>458</v>
+        <v>413</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>461</v>
+        <v>416</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>83</v>
@@ -7425,31 +6742,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>372</v>
+        <v>417</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>418</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>190</v>
+        <v>419</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
@@ -7457,31 +6774,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F5" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>469</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
@@ -7489,31 +6806,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>470</v>
+        <v>427</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>471</v>
+        <v>428</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>459</v>
+        <v>409</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>472</v>
+        <v>429</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>473</v>
+        <v>430</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
@@ -7521,31 +6838,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>475</v>
+        <v>432</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>462</v>
+        <v>414</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>476</v>
+        <v>433</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>477</v>
+        <v>434</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -7553,31 +6870,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>375</v>
+        <v>436</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>376</v>
+        <v>258</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="F8" s="3">
         <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>479</v>
+        <v>439</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>210</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -7585,28 +6902,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>465</v>
+        <v>427</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>481</v>
+        <v>441</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>44</v>
@@ -7617,31 +6934,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>483</v>
+        <v>249</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>484</v>
+        <v>178</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -7649,31 +6966,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>487</v>
+        <v>445</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F11" s="3">
         <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>488</v>
+        <v>446</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>489</v>
+        <v>447</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -7681,31 +6998,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>491</v>
+        <v>239</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>492</v>
+        <v>449</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>493</v>
+        <v>450</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>96</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -7713,31 +7030,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>494</v>
+        <v>427</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>495</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>230</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>496</v>
+        <v>452</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>44</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14">
@@ -7745,31 +7062,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>497</v>
+        <v>454</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>498</v>
+        <v>121</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>197</v>
+        <v>455</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>499</v>
+        <v>456</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>500</v>
+        <v>457</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>501</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15">
@@ -7777,31 +7094,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>503</v>
+        <v>459</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>119</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16">
@@ -7809,31 +7126,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>507</v>
+        <v>350</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>508</v>
+        <v>465</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>99</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17">
@@ -7841,31 +7158,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>219</v>
+        <v>469</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>511</v>
+        <v>470</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>512</v>
+        <v>471</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
@@ -7873,31 +7190,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>341</v>
+        <v>472</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>513</v>
+        <v>473</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>230</v>
+        <v>347</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="F18" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>514</v>
+        <v>474</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>515</v>
+        <v>475</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>339</v>
+        <v>463</v>
       </c>
     </row>
     <row r="19">
@@ -7905,31 +7222,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>70</v>
+        <v>477</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>516</v>
+        <v>478</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>518</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -7937,31 +7254,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>519</v>
+        <v>480</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>121</v>
+        <v>241</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>520</v>
+        <v>210</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
       <c r="F20" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>521</v>
+        <v>481</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>522</v>
+        <v>482</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>518</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -7969,31 +7286,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>523</v>
+        <v>483</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>524</v>
+        <v>484</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>385</v>
+        <v>204</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>525</v>
+        <v>485</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>526</v>
+        <v>486</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>527</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W25.xlsx
+++ b/reports/devops-jobs-israel-2026-W25.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-19T10:53:35</t>
+    <t xml:space="preserve">2026-06-21T10:02:12</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9%</t>
+    <t xml:space="preserve">2.7%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -159,10 +159,13 @@
     <t xml:space="preserve">Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4855504101?gh_jid=4855504101</t>
+    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4888525101?gh_jid=4888525101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
     <t xml:space="preserve">Lead DevOps Engineer</t>
@@ -177,15 +180,9 @@
     <t xml:space="preserve">Senior Cloud Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure, Networking, Security, AI/MLOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4883675101?gh_jid=4883675101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solution Architect</t>
   </si>
   <si>
@@ -228,6 +225,24 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI Cloud Architect</t>
   </si>
   <si>
@@ -486,157 +501,199 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; CloudOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-at-moveo-source-4427499835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4431365664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Yokneam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-yokneam-at-codevalue-4429938053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; IT Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contguard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-manager-at-contguard-4427327416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; AI Platform team lead - JB-680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-platform-team-lead-jb-680-at-pwc-next-technology-solutions-4428686942</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevSecOps</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cisco-4410016662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4421601376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; CloudOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloudops-at-moveo-source-4427499835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21936 - DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-4426800318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-amp-4429235005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-riverside-4427815913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
   </si>
   <si>
     <t xml:space="preserve">Logica-IT</t>
@@ -648,6 +705,36 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4430439283</t>
   </si>
   <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-ludeo-4418764125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4431363149</t>
+  </si>
+  <si>
     <t xml:space="preserve">comblack</t>
   </si>
   <si>
@@ -657,561 +744,504 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4430455192</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; AI Platform team lead - JB-680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-ai-platform-team-lead-jb-680-at-pwc-next-technology-solutions-4428686942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnyClip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile Group Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4429090109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist (36628)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4430455329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XM Cyber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridgify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Azure, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/aws-devops-engineer-at-abra-4430316804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finubit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-finubit-4428632503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4431378416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-ai-4425749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-hyro-4418385319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elementor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SessionCam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4430430529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-unity-4428813920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teva Pharmaceuticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekgence Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpticSolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-opticsolution-4427439160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technology Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technology-infrastructure-engineer-at-elbit-systems-israel-4399544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4429338126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/navigation-system-engineer-at-iai-israel-aerospace-industries-4425771548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYL Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-dyl-group-4428654157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-system-engineer-at-calanit-by-one-4431369529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-rafael-advanced-defense-systems-4429211666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Fend Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-d-fend-solutions-4429992083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead SRE, DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigPanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4427444455</t>
   </si>
   <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-gotfriends-4426809078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-lendbuzz-4417186999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4430900015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile Group Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mobile-group-ltd-4429090109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-sunbit-4428634522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist (36628)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-36628-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4430455329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4428846132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-planck-4427703990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4430450699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-utila-4429083966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Specialized Career Path (Prior Coding or IT Exp. Required)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-specialized-career-path-prior-coding-or-it-exp-required-at-infinitylabs-r-d-4429134082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4428874884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sunbit-4393297319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnyClip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-anyclip-4426846862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Intern ( Magshimim )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XM Cyber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-intern-magshimim-at-xm-cyber-4429504320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4407756951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4427304910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior CloudOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
   </si>
   <si>
     <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Azure | Kubernetes | Python | React)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridgify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Azure, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-azure-kubernetes-python-react-at-bridgify-4428851792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-unity-4428813920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior CloudOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloudops-engineer-at-hpe-aruba-networking-4429567275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-4399101600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finubit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-finubit-4428632503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4416339934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4427304910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4412804832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SessionCam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sessioncam-4430430529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4409713975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer- Yokneam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-yokneam-at-codevalue-4429938053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-planck-4427718090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Azure Platform &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAAT Delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-haat-delivery-4426484215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-azure-platform-devops-engineer-at-gini-apps-4428816993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elementor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-elementor-4429298687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jeen-ai-4430489121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-directeam-4427337476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4420455690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (DevSecOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teva Pharmaceuticals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-devsecops-at-teva-pharmaceuticals-4429916500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4427345124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-jobgether-4428039366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-extreme-4428823799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tekgence Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-infrastructure-engineer-at-tekgence-inc-4429373530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mPrest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4425720740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8 Stealth Mode Startup-Senior Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/team8-stealth-mode-startup-senior-infra-engineer-at-team8-4427476799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4429038091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4429338126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYL Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-dyl-group-4428654157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead SRE, DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigPanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-sre-devops-group-at-bigpanda-4427444455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NoTraffic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-notraffic-4430412124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-manager-at-finonex-4360108342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAAT Delivery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-haat-delivery-4426484215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
     <t xml:space="preserve">Terraform</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
+    <t xml:space="preserve">AI/MLOps</t>
   </si>
   <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus</t>
   </si>
   <si>
@@ -1230,10 +1260,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6%</t>
+    <t xml:space="preserve">54.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1257,6 +1287,12 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -1272,219 +1308,210 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
-    <t xml:space="preserve">SW DevOps and Test Infrastructure Student, Nitro SW Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer – Microsoft Infrastructure &amp; Cloud (Help Desk + 3rd Tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-MEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-%E2%80%93-microsoft-infrastructure-cloud-help-desk-%2B-3rd-tier-at-g-mel-4429114041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact Networks Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eilat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-impact-networks-group-4429545054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker, Kubernetes, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-dream-4427425550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-specialist-at-log-on-software-4425797474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Terraform/IaC, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-devops-and-test-infrastructure-student-nitro-sw-team-at-amazon-web-services-aws-4425403074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer (36613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-36613-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4428823042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Git</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1497,13 +1524,13 @@
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
@@ -1658,7 +1685,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -1666,7 +1693,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1674,7 +1701,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1682,7 +1709,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="10">
@@ -1690,7 +1717,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1754,7 +1781,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
@@ -1781,36 +1808,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>420</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1818,9 +1845,17 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>487</v>
+        <v>459</v>
       </c>
       <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1837,39 +1872,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -1877,90 +1912,90 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>392</v>
+        <v>502</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>493</v>
+        <v>401</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>299</v>
+        <v>503</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>494</v>
+        <v>399</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>388</v>
+        <v>297</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1985,13 +2020,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2">
@@ -2002,10 +2037,10 @@
         <v>37</v>
       </c>
       <c r="C2" s="3">
-        <v>18.4</v>
+        <v>13.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2014,88 +2049,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3">
-        <v>38.8</v>
+        <v>36.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>7.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.9</v>
+        <v>36.3</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.3</v>
+        <v>17.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2107,7 +2142,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2179,7 +2214,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -2211,7 +2246,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2240,15 +2275,15 @@
         <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>35</v>
@@ -2263,24 +2298,24 @@
         <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
@@ -2295,7 +2330,7 @@
         <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
@@ -2304,15 +2339,15 @@
         <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J6" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>
@@ -2327,147 +2362,147 @@
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J7" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="J8" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J10" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J11" s="3">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -2475,112 +2510,112 @@
         <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J13" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="J14" s="3">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>86</v>
@@ -2592,59 +2627,59 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="J15" s="3">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="J16" s="3">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>94</v>
@@ -2659,149 +2694,149 @@
         <v>96</v>
       </c>
       <c r="J17" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J18" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J19" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J20" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="J21" s="3">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>38</v>
@@ -2816,59 +2851,59 @@
         <v>114</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="J22" s="3">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J23" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>122</v>
@@ -2883,7 +2918,7 @@
         <v>124</v>
       </c>
       <c r="J24" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -2891,112 +2926,112 @@
         <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="J25" s="3">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="J26" s="3">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>139</v>
@@ -3008,88 +3043,88 @@
         <v>140</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="J29" s="3">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J30" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>38</v>
@@ -3104,118 +3139,118 @@
         <v>153</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="J31" s="3">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="J32" s="3">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J33" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J34" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>38</v>
@@ -3225,419 +3260,419 @@
         <v>24</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J35" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J36" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J37" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J38" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J39" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="J40" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>194</v>
+        <v>58</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J45" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3647,160 +3682,164 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>221</v>
+        <v>108</v>
       </c>
       <c r="J50" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>227</v>
+        <v>56</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J54" s="3">
         <v>0</v>
@@ -3808,76 +3847,76 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>235</v>
+        <v>137</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>38</v>
@@ -3887,27 +3926,27 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3917,27 +3956,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J58" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>64</v>
+        <v>248</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3947,250 +3986,250 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D61" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="J61" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>253</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>132</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>178</v>
+        <v>260</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="J63" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>132</v>
+        <v>262</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>60</v>
+        <v>265</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>204</v>
+        <v>70</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="J65" s="3">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>267</v>
+        <v>137</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>178</v>
+        <v>273</v>
       </c>
       <c r="D67" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="J67" s="3">
         <v>2</v>
@@ -4198,59 +4237,59 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="J68" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>88</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="J69" s="3">
         <v>26</v>
@@ -4258,106 +4297,106 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>60</v>
+        <v>265</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="J70" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>278</v>
+        <v>93</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D71" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="J71" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="J72" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>38</v>
@@ -4367,59 +4406,59 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>38</v>
@@ -4429,179 +4468,179 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J75" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>64</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="D76" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="J76" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>296</v>
+        <v>137</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>298</v>
+        <v>180</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>299</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>301</v>
+        <v>137</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>178</v>
+        <v>305</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>178</v>
+        <v>309</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>307</v>
+        <v>63</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4611,239 +4650,237 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>262</v>
+        <v>120</v>
       </c>
       <c r="J81" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>216</v>
+        <v>313</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J82" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>265</v>
+        <v>188</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>314</v>
+        <v>44</v>
       </c>
       <c r="J83" s="3">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>132</v>
+        <v>320</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="J85" s="3">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>319</v>
+        <v>137</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>138</v>
+        <v>236</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>323</v>
+        <v>137</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="D88" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>325</v>
-      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J88" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>38</v>
@@ -4853,10 +4890,10 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="J89" s="3">
         <v>2</v>
@@ -4864,89 +4901,91 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>329</v>
+        <v>63</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>44</v>
+        <v>182</v>
       </c>
       <c r="J90" s="3">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>132</v>
+        <v>333</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F91" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>45</v>
+        <v>336</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="D92" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="J92" s="3">
         <v>2</v>
@@ -4954,111 +4993,109 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>178</v>
+        <v>341</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>119</v>
+        <v>198</v>
       </c>
       <c r="J93" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="D94" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>341</v>
-      </c>
+      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="J94" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>132</v>
+        <v>307</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D95" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>347</v>
+        <v>235</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>138</v>
+        <v>236</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
@@ -5068,10 +5105,10 @@
         <v>348</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J96" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
@@ -5079,18 +5116,20 @@
         <v>349</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>350</v>
+        <v>304</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>210</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F97" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
@@ -5098,27 +5137,27 @@
         <v>351</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J97" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="D98" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
@@ -5128,10 +5167,10 @@
         <v>354</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="J98" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -5139,103 +5178,103 @@
         <v>355</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>60</v>
+        <v>265</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="J99" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>230</v>
+        <v>143</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="J100" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>281</v>
+        <v>363</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>178</v>
+        <v>364</v>
       </c>
       <c r="D101" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="J101" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>38</v>
@@ -5245,70 +5284,72 @@
         <v>23</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="J102" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>364</v>
+        <v>307</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>365</v>
+        <v>251</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>366</v>
+        <v>206</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="J103" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F104" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="G104" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J104" s="3">
         <v>0</v>
@@ -5316,76 +5357,76 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>178</v>
+        <v>373</v>
       </c>
       <c r="D105" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J105" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>222</v>
+        <v>375</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="D106" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="J106" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>38</v>
@@ -5395,57 +5436,57 @@
         <v>23</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J107" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D108" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J108" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>38</v>
@@ -5455,47 +5496,137 @@
         <v>23</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="J109" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>383</v>
+        <v>70</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="J110" s="3">
-        <v>0</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J111" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J112" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J113" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J110"/>
+  <autoFilter ref="A1:J113"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5606,6 +5737,9 @@
     <hyperlink ref="H108" r:id="rId107"/>
     <hyperlink ref="H109" r:id="rId108"/>
     <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5613,9 +5747,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5647,13 +5781,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5661,18 +5795,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5680,18 +5814,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5699,18 +5833,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>296</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5718,18 +5852,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5737,18 +5871,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>231</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>132</v>
+        <v>369</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>232</v>
+        <v>370</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5756,18 +5890,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>234</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>238</v>
+        <v>343</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>239</v>
+        <v>372</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>210</v>
+        <v>373</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5775,182 +5909,11 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5959,15 +5922,6 @@
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
     <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5981,63 +5935,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>387</v>
+        <v>297</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>325</v>
+        <v>399</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>390</v>
+        <v>172</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>170</v>
+        <v>350</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -6045,15 +5999,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>299</v>
+        <v>401</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -6061,23 +6015,23 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -6085,23 +6039,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -6123,7 +6077,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2">
@@ -6136,7 +6090,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -6144,7 +6098,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -6152,15 +6106,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>304</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6168,15 +6122,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>297</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6184,7 +6138,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -6192,7 +6146,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -6200,7 +6154,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -6208,7 +6162,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6216,7 +6170,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6224,7 +6178,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6232,7 +6186,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6240,7 +6194,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6261,16 +6215,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2">
@@ -6278,7 +6232,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3">
         <v>22.7</v>
@@ -6292,13 +6246,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="C3" s="3">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="D3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6306,13 +6260,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
-        <v>19.2</v>
+        <v>17.3</v>
       </c>
       <c r="D4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6320,7 +6274,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3">
         <v>10.9</v>
@@ -6334,13 +6288,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3">
-        <v>10.1</v>
+        <v>7.3</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6348,10 +6302,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C7" s="3">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -6362,13 +6316,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>121</v>
+        <v>304</v>
       </c>
       <c r="C8" s="3">
         <v>6.2</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6376,13 +6330,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>297</v>
+        <v>155</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6</v>
+        <v>5.0</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6390,7 +6344,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C10" s="3">
         <v>4.3</v>
@@ -6404,13 +6358,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6418,13 +6372,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6432,7 +6386,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -6446,7 +6400,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -6460,13 +6414,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6474,13 +6428,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>146</v>
+        <v>251</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6500,18 +6454,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6519,13 +6473,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4">
@@ -6533,10 +6487,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -6555,23 +6509,23 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6579,12 +6533,12 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6592,7 +6546,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6600,15 +6554,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6616,7 +6570,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6631,7 +6585,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6643,10 +6597,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6658,10 +6612,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6678,28 +6632,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>44</v>
@@ -6710,31 +6664,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>412</v>
+        <v>262</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>413</v>
+        <v>263</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>83</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
@@ -6742,31 +6696,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>419</v>
+        <v>70</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F4" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
@@ -6774,31 +6728,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F5" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -6806,31 +6760,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="F6" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -6838,31 +6792,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -6870,31 +6824,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>436</v>
+        <v>155</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="F8" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -6902,31 +6856,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>150</v>
+        <v>445</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F9" s="3">
         <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10">
@@ -6934,31 +6888,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>249</v>
+        <v>449</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>178</v>
+        <v>341</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F10" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>83</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -6966,31 +6920,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>222</v>
+        <v>453</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="F11" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -6998,31 +6952,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>239</v>
+        <v>457</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>210</v>
+        <v>458</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="F12" s="3">
         <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -7030,31 +6984,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F13" s="3">
         <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14">
@@ -7062,31 +7016,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F14" s="3">
         <v>30</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15">
@@ -7094,31 +7048,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>460</v>
+        <v>353</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F15" s="3">
         <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>463</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16">
@@ -7126,31 +7080,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>467</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17">
@@ -7158,31 +7112,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
@@ -7190,31 +7144,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>473</v>
+        <v>344</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>347</v>
+        <v>239</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19">
@@ -7222,31 +7176,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -7254,31 +7208,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>241</v>
+        <v>490</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>210</v>
+        <v>341</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21">
@@ -7286,31 +7240,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>484</v>
+        <v>246</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>437</v>
+        <v>494</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
